--- a/ProgramNotes/Database Notes/Database 1.xlsx
+++ b/ProgramNotes/Database Notes/Database 1.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30110"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Charlie\Non Puriel\Adress-Shack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4733EC11-5F02-409D-92BF-4625A861D9C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5223914A-20AF-453B-85CD-D56106D83657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="SampleData" sheetId="2" r:id="rId1"/>
-    <sheet name="Address Book" sheetId="1" r:id="rId2"/>
-    <sheet name="Snacks" sheetId="4" r:id="rId3"/>
-    <sheet name="Vending" sheetId="5" r:id="rId4"/>
-    <sheet name="Sales" sheetId="6" r:id="rId5"/>
+    <sheet name="Sample Data 2" sheetId="7" r:id="rId1"/>
+    <sheet name="SampleData" sheetId="2" r:id="rId2"/>
+    <sheet name="Address Book" sheetId="1" r:id="rId3"/>
+    <sheet name="Snacks" sheetId="4" r:id="rId4"/>
+    <sheet name="Vending" sheetId="5" r:id="rId5"/>
+    <sheet name="Sales" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -36,14 +37,104 @@
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
+      <xlwcv:version warnBelowVersion="2" setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="116">
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>H:\Students_Folder\Charlie Hatch\Semesters\Multi-Semester\App Dev\Projects\Advanced Appdev\Snack-Shack\presetImages\2fer.jpg</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>H:\Students_Folder\Charlie Hatch\Semesters\Multi-Semester\App Dev\Projects\Advanced Appdev\Snack-Shack\presetImages\airheads.jpg</t>
+  </si>
+  <si>
+    <t>testing</t>
+  </si>
+  <si>
+    <t>H:\Students_Folder\Charlie Hatch\Semesters\Multi-Semester\App Dev\Projects\Advanced Appdev\Snack-Shack\presetImages\extragum.jpg</t>
+  </si>
+  <si>
+    <t>tungsten</t>
+  </si>
+  <si>
+    <t>hi</t>
+  </si>
+  <si>
+    <t>this is a test</t>
+  </si>
+  <si>
+    <t>H:\Students_Folder\Charlie Hatch\Semesters\Multi-Semester\App Dev\Projects\Advanced Appdev\Snack-Shack\presetImages\almondjoy.png</t>
+  </si>
+  <si>
+    <t>H:\Students_Folder\Charlie Hatch\Semesters\Multi-Semester\App Dev\Projects\Advanced Appdev\Snack-Shack\presetImages\juicyfruit.jpg</t>
+  </si>
+  <si>
+    <t>tests</t>
+  </si>
+  <si>
+    <t>test2</t>
+  </si>
+  <si>
+    <t>w</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  12   124</t>
+  </si>
+  <si>
+    <t>testasae</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tests </t>
+  </si>
+  <si>
+    <t>charlie</t>
+  </si>
+  <si>
+    <t>hatch</t>
+  </si>
+  <si>
+    <t>this is a largeer scale test</t>
+  </si>
+  <si>
+    <t>large</t>
+  </si>
+  <si>
+    <t>this is a very large scale test and I do mean very as in very</t>
+  </si>
+  <si>
+    <t>test3</t>
+  </si>
+  <si>
+    <t>testt</t>
+  </si>
+  <si>
+    <t>4444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA</t>
+  </si>
+  <si>
+    <t>info</t>
+  </si>
   <si>
     <t>Index</t>
   </si>
@@ -109,9 +200,6 @@
   </si>
   <si>
     <t>Contains the phone number (with the normal phonenumber formating)</t>
-  </si>
-  <si>
-    <t>test</t>
   </si>
   <si>
     <t>email@email.email</t>
@@ -205,67 +293,10 @@
     <t>Not sure how, they got a soviute union website</t>
   </si>
   <si>
-    <t>testing</t>
-  </si>
-  <si>
-    <t>test2</t>
-  </si>
-  <si>
-    <t>tests</t>
-  </si>
-  <si>
-    <t>w</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  12   124</t>
-  </si>
-  <si>
-    <t>testasae</t>
-  </si>
-  <si>
-    <t>t</t>
-  </si>
-  <si>
-    <t>e</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>hi</t>
-  </si>
-  <si>
-    <t>h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tests </t>
-  </si>
-  <si>
-    <t>charlie</t>
-  </si>
-  <si>
-    <t>hatch</t>
-  </si>
-  <si>
-    <t>this is a largeer scale test</t>
-  </si>
-  <si>
-    <t>large</t>
-  </si>
-  <si>
-    <t>this is a very large scale test and I do mean very as in very</t>
-  </si>
-  <si>
-    <t>test3</t>
-  </si>
-  <si>
-    <t>testt</t>
-  </si>
-  <si>
-    <t>4444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444444AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA</t>
-  </si>
-  <si>
-    <t>info</t>
+    <t>size</t>
+  </si>
+  <si>
+    <t>?</t>
   </si>
   <si>
     <t>numeric</t>
@@ -280,10 +311,7 @@
     <t>bit</t>
   </si>
   <si>
-    <t>size</t>
-  </si>
-  <si>
-    <t>?</t>
+    <t>SnackID</t>
   </si>
   <si>
     <t>Name</t>
@@ -298,6 +326,12 @@
     <t>Image Path</t>
   </si>
   <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>Valid</t>
+  </si>
+  <si>
     <t>Field</t>
   </si>
   <si>
@@ -310,47 +344,65 @@
     <t>description</t>
   </si>
   <si>
+    <t>2fer.jpg</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>uuid for said entry</t>
+  </si>
+  <si>
+    <t>airheads.jpg</t>
+  </si>
+  <si>
+    <t>varchar(30)</t>
+  </si>
+  <si>
+    <t>name of the snack</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>smallmoney</t>
+  </si>
+  <si>
+    <t>price of snack</t>
+  </si>
+  <si>
+    <t>extragum.jpg</t>
+  </si>
+  <si>
     <t>Quantity</t>
   </si>
   <si>
-    <t>name of the snack</t>
-  </si>
-  <si>
-    <t>price of snack</t>
-  </si>
-  <si>
-    <t>int</t>
+    <t>tinyint</t>
   </si>
   <si>
     <t>quantity of snack</t>
   </si>
   <si>
+    <t>varchar(15)</t>
+  </si>
+  <si>
     <t>path of image</t>
   </si>
   <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>char(30)</t>
-  </si>
-  <si>
-    <t>smallmoney</t>
-  </si>
-  <si>
-    <t>tinyint</t>
-  </si>
-  <si>
-    <t>SnackID</t>
-  </si>
-  <si>
-    <t>uuid for said entry</t>
+    <t>almondjoy.png</t>
+  </si>
+  <si>
+    <t>juicyfruit.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -365,6 +417,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -388,7 +446,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -397,12 +455,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="4">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -423,7 +493,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{962C7140-9458-4E7F-884A-6E9A4E8487F2}" name="Table1" displayName="Table1" ref="A1:G11" totalsRowShown="0">
   <autoFilter ref="A1:G11" xr:uid="{962C7140-9458-4E7F-884A-6E9A4E8487F2}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{60AA6AD5-C93C-4B92-85FF-D77DD40E87A5}" name="Index" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{60AA6AD5-C93C-4B92-85FF-D77DD40E87A5}" name="Index" dataDxfId="3">
       <calculatedColumnFormula>IF(ISNUMBER(A1),A1+1,0)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{54099B7A-9B8C-482B-8083-4CA8C5275D84}" name="First Name"/>
@@ -438,23 +508,29 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A47B01E8-8101-4DDF-8AB7-5C5FCA655866}" name="Table2" displayName="Table2" ref="A1:E5" totalsRowShown="0">
-  <autoFilter ref="A1:E5" xr:uid="{A47B01E8-8101-4DDF-8AB7-5C5FCA655866}"/>
-  <tableColumns count="5">
-    <tableColumn id="5" xr3:uid="{16675459-3146-4AB1-AF33-2448F18FFD91}" name="SnackID"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A47B01E8-8101-4DDF-8AB7-5C5FCA655866}" name="Table2" displayName="Table2" ref="A1:G12" totalsRowShown="0">
+  <autoFilter ref="A1:G12" xr:uid="{A47B01E8-8101-4DDF-8AB7-5C5FCA655866}"/>
+  <tableColumns count="7">
+    <tableColumn id="5" xr3:uid="{16675459-3146-4AB1-AF33-2448F18FFD91}" name="SnackID" dataDxfId="2">
+      <calculatedColumnFormula>IF(ISNUMBER(A1),A1+1,1)</calculatedColumnFormula>
+    </tableColumn>
     <tableColumn id="1" xr3:uid="{E195EB5F-6D4B-42C3-8801-919637F30006}" name="Name"/>
-    <tableColumn id="2" xr3:uid="{4B91A874-5D42-4D28-8019-43E3F99D2B4B}" name="Price"/>
+    <tableColumn id="2" xr3:uid="{4B91A874-5D42-4D28-8019-43E3F99D2B4B}" name="Price" dataDxfId="1"/>
     <tableColumn id="3" xr3:uid="{191A4393-993C-4AB5-9310-5337B03C07D3}" name="Quantity On Hand"/>
     <tableColumn id="4" xr3:uid="{01AF8722-0E57-4D45-8F72-AD068B958406}" name="Image Path"/>
+    <tableColumn id="6" xr3:uid="{85B6F931-9CA9-4FF4-9FB1-406FC9E56BA6}" name="Column1"/>
+    <tableColumn id="7" xr3:uid="{AEC76C43-8C35-4A51-B34A-C477D5C7F079}" name="Valid" dataDxfId="0">
+      <calculatedColumnFormula>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -492,7 +568,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -598,7 +674,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -740,16 +816,16 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F28EEB29-88E9-4F91-A919-2DF8C70E2648}">
-  <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ECEA5BB-8E4E-42E6-AD28-A777D9306799}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
@@ -759,422 +835,191 @@
     <col min="7" max="7" width="3.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" t="s">
-        <v>22</v>
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>0.05</v>
       </c>
       <c r="C1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" t="b">
-        <v>1</v>
-      </c>
-      <c r="F1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B2" t="s">
-        <v>54</v>
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>0.7</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>0.05</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D4">
-        <v>11</v>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="C5">
+        <v>33</v>
+      </c>
+      <c r="D5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" t="s">
-        <v>58</v>
-      </c>
-      <c r="G5">
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="C6">
+        <v>97</v>
+      </c>
+      <c r="D6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" t="s">
-        <v>55</v>
-      </c>
-      <c r="G6">
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>0.08</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7">
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8">
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9" t="s">
-        <v>63</v>
+      <c r="B9">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>11</v>
-      </c>
-      <c r="E9" t="b">
-        <v>1</v>
-      </c>
-      <c r="F9" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10">
+        <v>0.05</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>1</v>
-      </c>
-      <c r="B10">
-        <v>2</v>
-      </c>
-      <c r="C10">
-        <v>4</v>
-      </c>
-      <c r="D10">
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11">
+        <v>0.05</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11" t="s">
         <v>3</v>
       </c>
-      <c r="E10" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>5</v>
-      </c>
-      <c r="G10">
+      <c r="E11">
         <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>59</v>
-      </c>
-      <c r="B11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" t="s">
-        <v>55</v>
-      </c>
-      <c r="G11">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>65</v>
-      </c>
-      <c r="B12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12">
-        <v>1234567891</v>
-      </c>
-      <c r="D12" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" t="b">
-        <v>1</v>
-      </c>
-      <c r="F12" t="s">
-        <v>67</v>
-      </c>
-      <c r="G12">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13">
-        <v>12</v>
-      </c>
-      <c r="D13" t="s">
-        <v>68</v>
-      </c>
-      <c r="E13" t="b">
-        <v>1</v>
-      </c>
-      <c r="F13" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14" t="s">
-        <v>70</v>
-      </c>
-      <c r="E14" t="b">
-        <v>1</v>
-      </c>
-      <c r="F14" t="s">
-        <v>59</v>
-      </c>
-      <c r="G14">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>71</v>
-      </c>
-      <c r="E15" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>59</v>
-      </c>
-      <c r="E16" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18">
-        <v>12</v>
-      </c>
-      <c r="D18" t="s">
-        <v>68</v>
-      </c>
-      <c r="E18" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" t="s">
-        <v>72</v>
-      </c>
-      <c r="G18">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>1</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19">
-        <v>1234567890</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19" t="b">
-        <v>0</v>
-      </c>
-      <c r="F19" t="s">
-        <v>73</v>
-      </c>
-      <c r="G19">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20" t="s">
-        <v>54</v>
-      </c>
-      <c r="E20" t="b">
-        <v>1</v>
-      </c>
-      <c r="F20" t="s">
-        <v>22</v>
-      </c>
-      <c r="G20">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1183,9 +1028,445 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F28EEB29-88E9-4F91-A919-2DF8C70E2648}">
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="2" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>11</v>
+      </c>
+      <c r="E4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>11</v>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+      <c r="G10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12">
+        <v>1234567891</v>
+      </c>
+      <c r="D12" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" t="s">
+        <v>28</v>
+      </c>
+      <c r="G18">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>1</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>1234567890</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19" t="b">
+        <v>0</v>
+      </c>
+      <c r="F19" t="s">
+        <v>29</v>
+      </c>
+      <c r="G19">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B20" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" t="s">
+        <v>2</v>
+      </c>
+      <c r="G20">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AC24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
@@ -1200,342 +1481,342 @@
     <col min="13" max="13" width="21.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="30">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="K1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="30">
       <c r="A2">
         <f t="shared" ref="A2:A11" si="0">IF(ISNUMBER(A1),A1+1,0)</f>
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="D2">
         <v>2345678901</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="K2" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="45">
       <c r="A3">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="D3">
         <v>2811111111</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" t="s">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="K3" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D4">
         <v>2209371286</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="K4" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="30">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="D5">
         <v>9876111121</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="K5" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="O5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="D6">
         <v>1291821021</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="K6" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="D7">
         <v>1234543201</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="D8">
         <v>1234562311</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="D9">
         <v>1234567812</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="D11">
         <v>2312121212</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29">
       <c r="A17" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29">
       <c r="A18" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D18">
         <v>10</v>
@@ -1544,68 +1825,68 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29">
       <c r="A19" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="E19" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="F19" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29">
       <c r="P23" s="1"/>
       <c r="W23" t="s">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="X23" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="Y23">
         <v>1</v>
       </c>
       <c r="Z23" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="AA23" t="b">
         <v>0</v>
       </c>
       <c r="AB23" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="AC23">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29">
       <c r="W24" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="X24" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="Y24">
         <v>2</v>
       </c>
       <c r="Z24" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="AA24" t="b">
         <v>1</v>
       </c>
       <c r="AB24" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="AC24">
         <v>3</v>
@@ -1634,117 +1915,359 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C7BC218-E894-43DE-BEC3-7A8A07868B41}">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.85546875" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K1" t="s">
+        <v>96</v>
+      </c>
+      <c r="L1" t="s">
+        <v>97</v>
+      </c>
+      <c r="M1" t="s">
         <v>98</v>
       </c>
-      <c r="B1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E1" t="s">
-        <v>83</v>
-      </c>
-      <c r="H1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J1" t="s">
-        <v>86</v>
-      </c>
-      <c r="K1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H2" t="s">
-        <v>98</v>
-      </c>
-      <c r="I2" t="s">
-        <v>91</v>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2">
+        <f t="shared" ref="A2:A5" si="0">IF(ISNUMBER(A1),A1+1,1)</f>
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G2" t="b">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
+        <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="K2" t="s">
+        <v>100</v>
+      </c>
+      <c r="L2" t="s">
+        <v>100</v>
+      </c>
+      <c r="M2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="4">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G3" t="b">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
+        <v>1</v>
+      </c>
+      <c r="J3" t="s">
+        <v>89</v>
+      </c>
+      <c r="K3" t="s">
+        <v>64</v>
+      </c>
+      <c r="L3" t="s">
+        <v>103</v>
+      </c>
+      <c r="M3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="D4">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H3" t="s">
-        <v>80</v>
-      </c>
-      <c r="I3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J3" t="s">
-        <v>95</v>
-      </c>
-      <c r="K3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H4" t="s">
-        <v>81</v>
-      </c>
-      <c r="I4" t="s">
-        <v>94</v>
+      <c r="G4" t="b">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
+        <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H5" t="s">
-        <v>88</v>
-      </c>
-      <c r="I5" t="s">
-        <v>91</v>
+        <v>105</v>
+      </c>
+      <c r="L4" t="s">
+        <v>106</v>
+      </c>
+      <c r="M4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="G5" t="b">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
+        <v>1</v>
       </c>
       <c r="J5" t="s">
+        <v>109</v>
+      </c>
+      <c r="K5" t="s">
+        <v>100</v>
+      </c>
+      <c r="L5" t="s">
+        <v>110</v>
+      </c>
+      <c r="M5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="5">
+        <f>IF(ISNUMBER(A5),A5+1,1)</f>
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D6">
+        <v>33</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G6" s="5" t="b">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
+        <v>92</v>
+      </c>
+      <c r="K6" t="s">
+        <v>64</v>
+      </c>
+      <c r="L6" t="s">
+        <v>112</v>
+      </c>
+      <c r="M6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="5">
+        <f>IF(ISNUMBER(A6),A6+1,1)</f>
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="4">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D7">
         <v>97</v>
       </c>
-      <c r="K5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H6" t="s">
-        <v>83</v>
-      </c>
-      <c r="I6" t="s">
-        <v>35</v>
-      </c>
-      <c r="J6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K6" t="s">
-        <v>93</v>
+      <c r="E7" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G7" s="5" t="b">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="5">
+        <f>IF(ISNUMBER(A7),A7+1,1)</f>
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0.08</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G8" s="5" t="b">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="5">
+        <f>IF(ISNUMBER(A8),A8+1,1)</f>
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="4">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="G9" s="5" t="b">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="5">
+        <f>IF(ISNUMBER(A9),A9+1,1)</f>
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="4">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="G10" s="5" t="b">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="5">
+        <f>IF(ISNUMBER(A10),A10+1,1)</f>
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="G11" s="5" t="b">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="5">
+        <f>IF(ISNUMBER(A11),A11+1,1)</f>
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G12" s="5" t="b">
+        <f>IF(NOT(LEN(Table2[[#This Row],[Image Path]])&gt;$L$7),TRUE(),_xlfn.CONCAT(FALSE(),": ",LEN(Table2[[#This Row],[Image Path]])))</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1755,19 +2278,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E27DB38-9B86-476F-ADB3-257C50139E20}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1932462C-482C-40F7-8C16-E10683B0C6A3}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
